--- a/cursos.xlsx
+++ b/cursos.xlsx
@@ -577,7 +577,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -659,7 +659,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -741,7 +741,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -905,7 +905,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1151,7 +1151,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1233,7 +1233,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1315,7 +1315,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1397,7 +1397,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1484,7 +1484,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1566,7 +1566,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1648,7 +1648,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1730,7 +1730,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1812,7 +1812,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1894,7 +1894,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1976,7 +1976,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2058,7 +2058,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2140,7 +2140,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2222,7 +2222,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2386,7 +2386,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2468,7 +2468,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2632,7 +2632,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2714,7 +2714,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2796,7 +2796,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2878,7 +2878,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2960,7 +2960,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3042,7 +3042,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3124,7 +3124,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3288,7 +3288,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3534,7 +3534,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3616,7 +3616,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3698,7 +3698,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3780,7 +3780,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3862,7 +3862,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4026,7 +4026,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4108,7 +4108,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4190,7 +4190,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4272,7 +4272,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4354,7 +4354,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4436,7 +4436,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4518,7 +4518,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4600,7 +4600,7 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4682,7 +4682,7 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4764,7 +4764,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4846,7 +4846,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4928,7 +4928,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5010,7 +5010,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5092,7 +5092,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5174,7 +5174,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5256,7 +5256,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5338,7 +5338,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5420,7 +5420,7 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5502,7 +5502,7 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5584,7 +5584,7 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5666,7 +5666,7 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5748,7 +5748,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5830,7 +5830,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5912,7 +5912,7 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5994,7 +5994,7 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6076,7 +6076,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6158,7 +6158,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6240,7 +6240,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6322,7 +6322,7 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6404,7 +6404,7 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6486,7 +6486,7 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6568,7 +6568,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6650,7 +6650,7 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6732,7 +6732,7 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6814,7 +6814,7 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6896,7 +6896,7 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6978,7 +6978,7 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7060,7 +7060,7 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7142,7 +7142,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7224,7 +7224,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7306,7 +7306,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7388,7 +7388,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7470,7 +7470,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7552,7 +7552,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7634,7 +7634,7 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7716,7 +7716,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7798,7 +7798,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7880,7 +7880,7 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7962,7 +7962,7 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8044,7 +8044,7 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8126,7 +8126,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8208,7 +8208,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8290,7 +8290,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8372,7 +8372,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8454,7 +8454,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8536,7 +8536,7 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8618,7 +8618,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8700,7 +8700,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8782,7 +8782,7 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8864,7 +8864,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8946,7 +8946,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9028,7 +9028,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -9110,7 +9110,7 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9192,7 +9192,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9356,7 +9356,7 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9438,7 +9438,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9520,7 +9520,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9602,7 +9602,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9684,7 +9684,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9766,7 +9766,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9848,7 +9848,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9930,7 +9930,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -10012,7 +10012,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -10094,7 +10094,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10176,7 +10176,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10258,7 +10258,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10340,7 +10340,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10422,7 +10422,7 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10504,7 +10504,7 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10586,7 +10586,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10668,7 +10668,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -10750,7 +10750,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10832,7 +10832,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10914,7 +10914,7 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10996,7 +10996,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11078,7 +11078,7 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -11160,7 +11160,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -11242,7 +11242,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -11324,7 +11324,7 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11406,7 +11406,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11488,7 +11488,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11570,7 +11570,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -11652,7 +11652,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -11734,7 +11734,7 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11816,7 +11816,7 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11898,7 +11898,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11980,7 +11980,7 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -12062,7 +12062,7 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -12144,7 +12144,7 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12226,7 +12226,7 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -12308,7 +12308,7 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -12390,7 +12390,7 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -12472,7 +12472,7 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -12554,7 +12554,7 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -12636,7 +12636,7 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -12718,7 +12718,7 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12800,7 +12800,7 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -12882,7 +12882,7 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -12964,7 +12964,7 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13046,7 +13046,7 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13128,7 +13128,7 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13210,7 +13210,7 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -13292,7 +13292,7 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13374,7 +13374,7 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -13456,7 +13456,7 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -13538,7 +13538,7 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -13620,7 +13620,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -13702,7 +13702,7 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -13784,7 +13784,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -13866,7 +13866,7 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -13948,7 +13948,7 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -14030,7 +14030,7 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -14112,7 +14112,7 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -14194,7 +14194,7 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -14276,7 +14276,7 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -14358,7 +14358,7 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -14440,7 +14440,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -14522,7 +14522,7 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -14604,7 +14604,7 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -14686,7 +14686,7 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -14768,7 +14768,7 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -14850,7 +14850,7 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -14932,7 +14932,7 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -15014,7 +15014,7 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -15096,7 +15096,7 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -15178,7 +15178,7 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -15260,7 +15260,7 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -15342,7 +15342,7 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -15424,7 +15424,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -15502,7 +15502,7 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -15584,7 +15584,7 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -15666,7 +15666,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -15748,7 +15748,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -15830,7 +15830,7 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -15912,7 +15912,7 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -15994,7 +15994,7 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -16076,7 +16076,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -16158,7 +16158,7 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -16240,7 +16240,7 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -16322,7 +16322,7 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -16404,7 +16404,7 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -16486,7 +16486,7 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -16568,7 +16568,7 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -16650,7 +16650,7 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -16732,7 +16732,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -16896,7 +16896,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -16978,7 +16978,7 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -17060,7 +17060,7 @@
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -17142,7 +17142,7 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -17163,7 +17163,7 @@
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
-          <t>20 horas</t>
+          <t>64 horas</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -17224,7 +17224,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -17306,7 +17306,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -17388,7 +17388,7 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -17470,7 +17470,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -17552,7 +17552,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -17634,7 +17634,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -17716,7 +17716,7 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -17798,7 +17798,7 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -17880,7 +17880,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -17962,7 +17962,7 @@
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -18044,7 +18044,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
